--- a/www/download/COUNTRY.SVN.rpA2.xlsx
+++ b/www/download/COUNTRY.SVN.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>Eslovênia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.49387592371311</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.564464649528101</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.659121935129566</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.692520748907331</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.756629938465452</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.92447928619047</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.01182824043428</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.00081058753711</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.863125422093881</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.802021157505804</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.802903282049704</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.796438372834759</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.729659977856526</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.679902081177344</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.716948718120329</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.918</t>
+          <t>1.49386261344113</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.57320270242001</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>1.88719859136232</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>1.75913934381993</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>1.7891594489827</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>1.71124852416698</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>1.55443626527778</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>1.56003166484462</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>1.35807305875713</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>1.44530816031597</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.55756940146654</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>1.67642214520546</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.962</t>
+          <t>1.74857916044533</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.994</t>
+          <t>1.08163340573468</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>1.06860296136363</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>1.0313778783209</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>1.08130674935741</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>1.31952795164503</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>1.21320112619477</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>1.18941073050894</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>1.239930997898</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>1.13458430830955</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>1.10902390671242</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>0.907046418816926</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>0.965753814824007</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.05004509640679</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>1.03174085752571</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>1.07392814852191</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>0.550637475794789</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>0.560571472046865</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1708.758</t>
+          <t>0.151797902714224</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1670.15</t>
+          <t>0.178593496155029</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1638.628</t>
+          <t>0.334670706671778</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1629.509</t>
+          <t>0.268326645792834</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1644.428</t>
+          <t>0.308161666758874</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1660.151</t>
+          <t>0.279657332388652</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1662.069</t>
+          <t>0.22008848087851</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1682.333</t>
+          <t>0.179758439624519</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1671.121</t>
+          <t>0.068008418982018</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1671.611</t>
+          <t>0.107667941777613</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1664.697</t>
+          <t>0.146475937799328</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1689.328</t>
+          <t>0.141142756846958</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1740.358</t>
+          <t>0.0804114852121212</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1819.538</t>
+          <t>-0.16957071420536</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1778.476</t>
+          <t>-0.141562558393333</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1287.888</t>
+          <t>5839508198.11613</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1269.261</t>
+          <t>5683531627.25694</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1237.461</t>
+          <t>5351092744.99548</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1237.419</t>
+          <t>5420223891.33928</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1255.282</t>
+          <t>5518581970.03752</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1280.997</t>
+          <t>5783040707.98232</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1294.77</t>
+          <t>5671645910.7369</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1311.437</t>
+          <t>5749053622.65361</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1313.919</t>
+          <t>6167080422.86422</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1319.254</t>
+          <t>6275236509.27358</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1322.093</t>
+          <t>6277315690.10473</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1343.542</t>
+          <t>6532267784.20084</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1387.787</t>
+          <t>6853087561.57858</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1430.053</t>
+          <t>7381216538.66001</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1393.705</t>
+          <t>6551368402.08151</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>1789911670.67225</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>1724644974.19368</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>1507537625.08461</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>1582070102.65685</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>1625367829.1171</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>1669762218.61143</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>1727927270.07706</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>1791625487.30206</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28.58</t>
+          <t>2030120894.87491</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>1993431319.69058</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>1934688798.47672</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>1966973722.97779</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>2000220228.00933</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>2739730025.24432</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>34.16</t>
+          <t>2688977900.7358</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>5000826.77998642</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>4886822.18448519</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>4750691.99449258</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>4671621.0713492</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>62.86</t>
+          <t>4930795.35859703</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>60.34</t>
+          <t>5299279.96759229</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>63.84</t>
+          <t>5154736.12176177</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>62.09</t>
+          <t>4815560.85444978</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>60.03</t>
+          <t>4321522.29500919</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>59.41</t>
+          <t>3781569.29003648</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>3535877.75849883</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>3349585.02692611</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>2821202.89325477</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>2699418.29157991</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>2888607.03427084</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12626.2186356788</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>12156.0842781236</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>11751.5002184983</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>11491.7464780939</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>12045.8230235851</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>12452.8667339004</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>11539.4801083123</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>11831.1631184474</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>12940.4317627765</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>14265.3567330299</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>15296.6207929045</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>16201.7568121444</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>18578.1296875997</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>21545.4136535989</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>19585.4941112136</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>25472.8067641516</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>24716.702524909</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>22887.3548821767</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>22897.2929675652</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>24052.7395055928</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>25349.1575992805</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>27.41</t>
+          <t>23982.1930341538</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>24622.0217030519</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>28278.6179875513</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>31208.9665044608</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>33206.8577200151</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>37.48</t>
+          <t>35964.9395269212</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>42298.1455941635</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>39.56</t>
+          <t>49767.3712761747</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>40828.4603465209</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>62.62</t>
+          <t>1.08353875021367</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>62.62</t>
+          <t>1.14344564153807</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>62.62</t>
+          <t>1.40099001407831</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.62</t>
+          <t>1.29286644791111</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>62.41</t>
+          <t>1.30976078301587</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>60.59</t>
+          <t>1.32100165305759</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>64.88</t>
+          <t>1.17536749873982</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>1.17103191473039</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1.00072082372353</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>58.86</t>
+          <t>1.07995604063305</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>1.18089754786991</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>1.22494227721589</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>56.76</t>
+          <t>1.26602568575699</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>0.707323504047564</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>53.53</t>
+          <t>0.723940969695169</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>4600.07350075678</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>4509.21042852256</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>4316.10353506834</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>4747.61153442491</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>4803.44439850744</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>4146.60082110677</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>4191.53133922894</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>4462.08020053235</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>5586.82484942675</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>6778.10119338425</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>7120.80529720394</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>7703.03613571858</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>8850.07892662694</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>10928.0606762985</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>7715.81201843587</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.49387592371311</t>
+          <t>2413.74048537761</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.564464649528101</t>
+          <t>2359.44715213383</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.659121935129566</t>
+          <t>2112.67549145226</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.692520748907331</t>
+          <t>2217.14766173719</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.756629938465452</t>
+          <t>2246.47566838894</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.92447928619047</t>
+          <t>2261.19004096645</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.01182824043428</t>
+          <t>2316.5979837202</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.00081058753711</t>
+          <t>2371.10758278054</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.863125422093881</t>
+          <t>2684.19827887677</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.802021157505804</t>
+          <t>2625.4128166844</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.802903282049704</t>
+          <t>2544.47135986942</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796438372834759</t>
+          <t>2546.80146592302</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729659977856526</t>
+          <t>2509.34027676146</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902081177344</t>
+          <t>3338.28848974389</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948718120329</t>
+          <t>3359.01382433025</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>257540606.584664</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>347796829.774198</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>191689373.219331</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>327614967.695826</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>323442709.967231</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>385718288.331813</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>589753064.522645</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>826275890.792275</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1085504362.74776</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>826572535.080584</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>787122499.718639</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>887602241.503114</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1055081751.3458</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1630016439.24264</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1681772797.93591</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>333453130.468013</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>414019576.490236</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>255541217.220717</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>409481890.81472</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>407531942.911807</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>458813157.443646</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>686784318.167967</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>927867910.509917</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1224165173.95208</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>914007753.800875</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>902508292.287488</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>985795075.942221</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>1156903161.96711</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1668110544.35277</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>1738258305.96509</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>-75912523.8833497</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>-66222746.7160381</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>-63851844.0013864</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>-81866923.1188947</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>-84089232.9445767</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>-73094869.1118323</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>-97031253.6453225</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>-101592019.717643</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>-138660811.204316</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>-87435218.7202916</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>-115385792.568849</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>-98192834.4391075</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>-101821410.621306</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>-38094105.1101243</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>-56485508.0291871</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>5029.12183424378</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>5057.34671468065</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>5072.51275796487</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>5083.62348366177</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>5188.82139884414</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>5248.22582296049</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>5039.45196143112</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>5147.75023547578</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>5370.33139155161</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>5460.74324721815</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>5549.23134936444</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>5666.48625320753</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>5686.22952144602</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>5699.53840183119</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>5790.74154953537</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>5004.6038840587</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>5034.66630232677</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>5054.9244809798</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>5062.43910677456</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>5142.70253320082</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>5226.3869123159</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>5037.34205372642</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>5148.366200611</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>5368.93282415725</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>5453.05657145077</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>5513.5207085182</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>5634.67669902145</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>5676.87952058297</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>5758.89912300811</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>5881.92136060357</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>149.39</t>
+          <t>9272.3561394543</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>157.32</t>
+          <t>9285.34225976318</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>188.72</t>
+          <t>9365.768802039</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>175.91</t>
+          <t>10013.910562401</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>178.92</t>
+          <t>9573.69797367611</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>171.12</t>
+          <t>9813.22345086639</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>155.44</t>
+          <t>10317.846404815</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>11657.1211508588</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>135.81</t>
+          <t>14287.0125469065</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>144.53</t>
+          <t>18044.2917899178</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>155.76</t>
+          <t>20166.8374977181</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>167.64</t>
+          <t>23576.8940889948</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>174.86</t>
+          <t>29219.0397060095</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>108.16</t>
+          <t>32166.3406084947</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>106.86</t>
+          <t>24932.8159572924</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>1705790849.98761</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>108.13</t>
+          <t>1620051876.56471</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>131.95</t>
+          <t>1574681166.54735</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>121.32</t>
+          <t>1633565869.91969</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>118.94</t>
+          <t>1663319834.94929</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>123.99</t>
+          <t>1809211118.19744</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>113.46</t>
+          <t>1825425712.5381</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>110.9</t>
+          <t>1896334865.44826</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>2028596218.7802</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>96.58</t>
+          <t>2204608551.78643</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>2311566345.91506</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>103.17</t>
+          <t>2511014269.65181</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>107.39</t>
+          <t>2630111613.04983</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>55.06</t>
+          <t>2817681086.74239</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>56.06</t>
+          <t>2328422288.53431</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>9797.41148269065</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>9722.74805747548</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>9752.39271097419</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>26.83</t>
+          <t>10389.181562587</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>10471.0286433887</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>27.97</t>
+          <t>10541.5333387254</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>10558.6099646328</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>11480.3334118506</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>14456.1382515723</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>18654.9436607727</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>20708.9772832165</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>24089.404044779</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>30342.3600938279</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>34397.0564148913</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>24863.4479545927</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4594.722</t>
+          <t>2114325527.44334</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4528.753</t>
+          <t>2090960662.22206</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4461.456</t>
+          <t>1867583073.12083</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4460.019</t>
+          <t>2065732821.19594</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4593.169</t>
+          <t>2246387310.42634</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4728.338</t>
+          <t>2410236114.44132</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4578.486</t>
+          <t>2490583807.30644</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4751.067</t>
+          <t>2667339637.34943</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4935.3</t>
+          <t>3164177440.34883</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>5028.209</t>
+          <t>3198821441.23458</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>5074.165</t>
+          <t>3237304267.01067</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>5263.69</t>
+          <t>3519046899.87355</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>5462.64</t>
+          <t>3919536998.70233</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>5725.683</t>
+          <t>4868596634.62755</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>5727.967</t>
+          <t>3995599240.23483</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3729.35</t>
+          <t>-525.055343236346</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3696.683</t>
+          <t>-437.405797712301</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3619.583</t>
+          <t>-386.623908935183</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3627.475</t>
+          <t>-375.271000185987</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3754.211</t>
+          <t>-897.330669712611</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3875.521</t>
+          <t>-728.309887858981</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3758.877</t>
+          <t>-240.763559817807</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3889.676</t>
+          <t>176.787739008212</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4061.705</t>
+          <t>-169.125704665741</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4146.25</t>
+          <t>-610.651870854832</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>4219.358</t>
+          <t>-542.139785498375</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>4376.403</t>
+          <t>-512.509955784204</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4532.55</t>
+          <t>-1123.32038781845</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>4677.605</t>
+          <t>-2230.71580639669</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>4635.639</t>
+          <t>69.3680026997011</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5839.508</t>
+          <t>-408534677.455727</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5683.532</t>
+          <t>-470908785.657348</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5351.093</t>
+          <t>-292901906.573478</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>5420.224</t>
+          <t>-432166951.276254</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5518.582</t>
+          <t>-583067475.477046</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5783.041</t>
+          <t>-601024996.243876</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5671.646</t>
+          <t>-665158094.768347</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>5749.054</t>
+          <t>-771004771.901164</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6167.08</t>
+          <t>-1135581221.56864</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>6275.237</t>
+          <t>-994212889.448147</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>6277.316</t>
+          <t>-925737921.09561</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>6532.268</t>
+          <t>-1008032630.22174</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>6853.088</t>
+          <t>-1289425385.6525</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>7381.217</t>
+          <t>-2050915547.88516</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>6551.368</t>
+          <t>-1667176951.70053</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>9468.17638</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>9553.40543</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>9503.65261</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>10003.98798</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>10064.26296</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>9203.21878</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>9365.37753</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>10408.59163</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>13025.09187</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>15081.76118</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>15889.79686</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>17210.51997</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>20880.94144</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>23843.3406</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>20616.80425</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2894.495</t>
+          <t>-0.041061753482446</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2795.255</t>
+          <t>-0.0232466507270213</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2747.516</t>
+          <t>-0.00421681301572432</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2720.315</t>
+          <t>-0.00316315231198634</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2763.754</t>
+          <t>0.00318328148197952</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2840.94</t>
+          <t>0.009974022444106</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2729.018</t>
+          <t>0.0121147989031757</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2762.486</t>
+          <t>0.0199044730849146</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2822.086</t>
+          <t>0.0251690488199995</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2868.358</t>
+          <t>0.0201349470352987</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2891.623</t>
+          <t>0.0230952996990488</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2942.705</t>
+          <t>0.0270879158919468</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>3010.003</t>
+          <t>0.0358211088506305</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3195.495</t>
+          <t>0.0219737183329742</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3142.705</t>
+          <t>0.0322525832681607</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>11620.1369238212</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11384.3056424847</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>10709.4891936987</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11083.3810905755</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11180.7760355203</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>10295.4488956846</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>10625.4286805587</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11845.1108065973</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14830.0951715441</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>17269.3779092422</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>18247.4300526506</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>19678.4004124698</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>23588.5602801829</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>27890.5342784981</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>26281.4710697563</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1789.912</t>
+          <t>14964.620379661</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1724.645</t>
+          <t>14513.5561779957</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1507.538</t>
+          <t>13648.5087300115</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1582.07</t>
+          <t>14067.2700511963</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1625.368</t>
+          <t>14138.4792389739</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1669.762</t>
+          <t>12828.319893295</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1727.927</t>
+          <t>13125.6410110016</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1791.625</t>
+          <t>14692.7626133391</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2030.121</t>
+          <t>18237.6396378539</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1993.431</t>
+          <t>21236.2686187478</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1934.689</t>
+          <t>22383.7224061932</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1966.974</t>
+          <t>24088.5110512577</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2000.22</t>
+          <t>28899.233180043</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2739.73</t>
+          <t>34279.4176577063</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2688.978</t>
+          <t>32150.0842224023</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>108.35</t>
+          <t>42389.9215887585</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>114.34</t>
+          <t>42892.9633015573</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>140.1</t>
+          <t>41831.5572499992</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>129.29</t>
+          <t>45361.851554707</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>130.98</t>
+          <t>46489.8323809797</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>132.1</t>
+          <t>43248.2268829437</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>117.54</t>
+          <t>44081.1831907078</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>117.1</t>
+          <t>48971.3232784494</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>100.07</t>
+          <t>62434.2065509712</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>75315.7892697419</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>118.09</t>
+          <t>81725.3394066407</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>122.49</t>
+          <t>88550.1288689718</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>126.6</t>
+          <t>107022.898406523</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>70.73</t>
+          <t>134173.403031698</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>72.39</t>
+          <t>98881.1982173894</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5.001</t>
+          <t>14964.620379661</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4.887</t>
+          <t>15003.2649727884</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4.751</t>
+          <t>14922.9701872133</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4.672</t>
+          <t>15173.4962760684</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.931</t>
+          <t>15701.9804444718</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.299</t>
+          <t>16350.3662923365</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5.155</t>
+          <t>16979.3258268696</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4.816</t>
+          <t>17620.7621463449</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>4.322</t>
+          <t>17819.490583779</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.782</t>
+          <t>18610.3620447041</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3.536</t>
+          <t>19259.8288859295</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>20137.8783819463</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.821</t>
+          <t>21070.3153595469</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.699</t>
+          <t>22344.5842434324</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.889</t>
+          <t>21485.7949799498</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>11620.1369238212</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>11656.7466722342</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>11612.5759383847</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>11892.5620345832</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>12250.8383044423</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>12994.5453810855</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>13546.5762940706</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>14024.1579924517</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>14282.7705288857</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>14978.350651655</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>15666.1699242002</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>16387.9639260992</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>17339.2450984101</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>18317.4158893551</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>17673.1445639795</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2859.46899033896</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3512.09269200432</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4139.70767998852</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4604.12508880365</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>4951.43462102615</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4577.95960670504</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4725.56600899841</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>5436.8285866609</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>7158.23444214607</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>8294.58062125223</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>9008.27650380679</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>10101.6745787423</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>12683.757819957</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>13876.3492422936</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>10904.9860975977</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3729350325.30531</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3696682753.13597</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3619582783.67547</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3627475456.62517</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3754210869.67031</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3875520869.61024</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3758876823.51186</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3889676112.17715</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>4061705149.05249</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>4146249514.97753</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>4219358056.48926</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>4376402994.42602</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4532550413.83984</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>4677605466.84445</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>4635639169.68335</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4594721821.3504</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4528752824.27117</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4461456127.21485</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4460018977.9466</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>4593168768.61058</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>4728338371.50675</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4578485528.71043</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>4751066780.90985</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>4935300226.74854</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>5028208933.96904</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>5074164783.81851</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>5263689585.15788</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>5462639764.35569</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>5725683054.83116</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>5727967016.72911</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2894494820.17884</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2795255127.12261</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2747515730.22485</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2720314532.4651</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2763754279.91321</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2840939978.8208</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2729018362.71325</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2762486038.17472</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2822085698.2035</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2868357956.55474</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2891623125.51499</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2942705186.31641</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3010003102.76135</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3195494548.21917</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3142704529.39801</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>918099</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>899514</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>882596</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>881002</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>893143</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>904705</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>908909</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>922830</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>919233</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>922090</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>920313</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>934160</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>962261</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>994232.219132951</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>973825.841177403</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>741551</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>730953</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>713568</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>713561</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>723519</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>738444</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>745890</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>755607</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>756323</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>759283</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>760350</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>772331</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>797110</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>820699</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>800526</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1708757625.80647</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1670150120.2685</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1638627648.55927</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1629509098.6178</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1644428387.08447</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1660151050.6775</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1662068675.97344</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1682333193.89346</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1671120525.92652</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1671610829.04208</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1664696902.32574</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1689328102.08285</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1740358030.68536</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1819537674.08294</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1778476269.73853</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1287887658.44177</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1269260505.82646</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1237460870.20158</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1237419425.58602</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1255281960.24692</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1280996781.98652</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1294769820.60965</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1311436755.34495</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1313919474.72281</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1319253617.09501</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1322092727.88369</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1343541682.80064</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1387787215.2592</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1430053445.43154</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1393704986.53083</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.246865638342609</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.246865638342609</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.246865638342609</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.246865638342609</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.257023267552655</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.279413119243087</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.230621348589472</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.257362321072398</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.285823508591103</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.300466154223845</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.30899248679988</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.31293809402232</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.314209084368503</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.321657071696235</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.341631791924359</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.624435919070539</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.624435919070539</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.624435919070539</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.624435919070539</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.628636805898128</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.603415954512167</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.63837916359736</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.620910986397626</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.600341285626231</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.594092410633173</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.590468665356388</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.592062285047216</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.58441641414411</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.58000538446106</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.566979901880087</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.128698442586853</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.128698442586853</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.128698442586853</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.128698442586853</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.114339926549217</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.117170926244746</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.130999487813169</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.121726692529977</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.113835205782666</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.105441435142982</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.100538847843732</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0949996209304649</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.101374501487387</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0983375438427051</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0913883061955541</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.29767061222955</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.29767061222955</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.29767061222955</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.29767061222955</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.307668897508627</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.326605282690006</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.274140714955531</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.303511778976121</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.336187638665282</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.352645588588238</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.361457514461163</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.374785132924547</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.380563311562413</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.395559408618554</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.418147249194264</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.626242944328873</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.626242944328873</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.626242944328873</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.626242944328873</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.624111470054713</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.605906997475185</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.64876871144112</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.627470352165021</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.599965997808565</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.588610460310025</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.582896068714795</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.573375334147349</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.567629617472114</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.554090086471366</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.535256145902856</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0760864434415775</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0760864434415775</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0760864434415775</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0760864434415775</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0682196324366602</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0674877198348091</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0770905736033491</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0690178688588584</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0638463635261535</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.058743951101737</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0556464168240416</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0518395329281038</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0518070709654731</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0503505049100802</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0465966049028802</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>40260.23086</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>40779.67183</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>39685.83759</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>41536.33577</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>41819.65685</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>39411.53714</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>40018.74467</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>44922.06561</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>56083.43718</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>65875.94685</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>70482.11437</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>78329.00244</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>97551.78466</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>112680.84917</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>95937.80408</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>17824.08937</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>18025.64887</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>17788.21641</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>18671.39514</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>19089.91386</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>17406.2795</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>17851.20702</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>20129.5912</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>25395.87408</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>29530.84924</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>31391.99891</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>34190.18563</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>41582.991</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>48155.7669</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>43055.07032</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>20935.3616311307</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>22242.2910994064</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>23780.3187472429</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>25466.5858163651</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>27496.1382046508</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>29446.0190245068</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>31307.6121063329</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>33038.5226663467</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>34925.1672613311</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>36925.5782712133</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>38932.9585921994</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>41245.4571810376</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>44221.4509312072</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>49870.5902665899</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>38591.9125511486</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
